--- a/inst/extdata/potato_db.xlsx
+++ b/inst/extdata/potato_db.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kimbrel1/Github/gator/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kimbrel1/Github/potato/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE2F4179-84A9-E144-87A6-E6E92C7E6135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69FF315E-6CF5-064E-B0DA-D9BF5D228100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34980" yWindow="500" windowWidth="33840" windowHeight="28300" activeTab="1" xr2:uid="{CED2E7C7-DFF3-F648-B190-1601735D45BC}"/>
+    <workbookView xWindow="34960" yWindow="600" windowWidth="33840" windowHeight="28200" activeTab="2" xr2:uid="{CED2E7C7-DFF3-F648-B190-1601735D45BC}"/>
   </bookViews>
   <sheets>
     <sheet name="db" sheetId="1" r:id="rId1"/>
@@ -7932,7 +7932,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -7987,6 +7987,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -8001,7 +8007,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -8064,6 +8070,15 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -11224,7 +11239,7 @@
       <c r="G139" s="16" t="s">
         <v>528</v>
       </c>
-      <c r="H139" s="16" t="s">
+      <c r="H139" s="26" t="s">
         <v>520</v>
       </c>
       <c r="I139" s="16" t="s">
@@ -11253,7 +11268,7 @@
       <c r="G140" s="16" t="s">
         <v>528</v>
       </c>
-      <c r="H140" s="16" t="s">
+      <c r="H140" s="26" t="s">
         <v>521</v>
       </c>
     </row>
@@ -11276,7 +11291,7 @@
       <c r="G141" s="16" t="s">
         <v>528</v>
       </c>
-      <c r="H141" s="16" t="s">
+      <c r="H141" s="26" t="s">
         <v>522</v>
       </c>
     </row>
@@ -11299,7 +11314,7 @@
       <c r="G142" s="16" t="s">
         <v>536</v>
       </c>
-      <c r="H142" s="16" t="s">
+      <c r="H142" s="26" t="s">
         <v>523</v>
       </c>
       <c r="I142" s="16" t="s">
@@ -11325,7 +11340,7 @@
       <c r="G143" s="16" t="s">
         <v>536</v>
       </c>
-      <c r="H143" s="16" t="s">
+      <c r="H143" s="26" t="s">
         <v>524</v>
       </c>
       <c r="I143" s="16" t="s">
@@ -19764,7 +19779,7 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="56">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="25" t="s">
         <v>1133</v>
       </c>
       <c r="B2" s="12" t="s">
@@ -19775,7 +19790,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" ht="28">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="25" t="s">
         <v>1134</v>
       </c>
       <c r="B3" s="11" t="s">
@@ -19808,7 +19823,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="42">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="25" t="s">
         <v>1137</v>
       </c>
       <c r="B6" s="11" t="s">
@@ -19896,7 +19911,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" ht="42">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="25" t="s">
         <v>887</v>
       </c>
       <c r="B14" s="12" t="s">
@@ -19907,7 +19922,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" ht="14">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="25" t="s">
         <v>890</v>
       </c>
       <c r="B15" s="11" t="s">
@@ -19918,7 +19933,7 @@
       </c>
     </row>
     <row r="16" spans="1:4" ht="28">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="25" t="s">
         <v>891</v>
       </c>
       <c r="B16" s="11" t="s">
@@ -19929,7 +19944,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" ht="70">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="25" t="s">
         <v>892</v>
       </c>
       <c r="B17" s="11" t="s">
@@ -19940,7 +19955,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" ht="14">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="25" t="s">
         <v>888</v>
       </c>
       <c r="B18" s="11" t="s">
@@ -19951,7 +19966,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="14">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="25" t="s">
         <v>1167</v>
       </c>
       <c r="B19" s="11" t="s">
@@ -19959,7 +19974,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="14">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="25" t="s">
         <v>889</v>
       </c>
       <c r="B20" s="11" t="s">
@@ -19970,7 +19985,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" ht="28">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="25" t="s">
         <v>1336</v>
       </c>
       <c r="B21" s="11" t="s">
@@ -19981,7 +19996,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="14">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="25" t="s">
         <v>1179</v>
       </c>
       <c r="B22" s="11" t="s">
@@ -20173,7 +20188,7 @@
       </c>
     </row>
     <row r="42" spans="1:4" ht="14">
-      <c r="A42" s="11" t="s">
+      <c r="A42" s="25" t="s">
         <v>500</v>
       </c>
       <c r="B42" s="11" t="s">
@@ -20184,7 +20199,7 @@
       </c>
     </row>
     <row r="43" spans="1:4" ht="28">
-      <c r="A43" s="11" t="s">
+      <c r="A43" s="27" t="s">
         <v>540</v>
       </c>
       <c r="B43" s="11" t="s">
@@ -20195,7 +20210,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" ht="42">
-      <c r="A44" s="11" t="s">
+      <c r="A44" s="25" t="s">
         <v>566</v>
       </c>
       <c r="B44" s="11" t="s">
@@ -20206,7 +20221,7 @@
       </c>
     </row>
     <row r="45" spans="1:4" ht="28">
-      <c r="A45" s="11" t="s">
+      <c r="A45" s="27" t="s">
         <v>597</v>
       </c>
       <c r="B45" s="11" t="s">
@@ -20217,7 +20232,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" ht="28">
-      <c r="A46" s="11" t="s">
+      <c r="A46" s="27" t="s">
         <v>598</v>
       </c>
       <c r="B46" s="11" t="s">

--- a/inst/extdata/potato_db.xlsx
+++ b/inst/extdata/potato_db.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kimbrel1/Github/potato/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69FF315E-6CF5-064E-B0DA-D9BF5D228100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F9A319-F7E5-A546-B30C-4896F59BC882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="34960" yWindow="600" windowWidth="33840" windowHeight="28200" activeTab="2" xr2:uid="{CED2E7C7-DFF3-F648-B190-1601735D45BC}"/>
   </bookViews>
@@ -20874,7 +20874,7 @@
       </c>
     </row>
     <row r="98" spans="1:4" ht="84">
-      <c r="A98" s="8" t="s">
+      <c r="A98" s="25" t="s">
         <v>2315</v>
       </c>
       <c r="B98" s="8" t="s">
@@ -20888,7 +20888,7 @@
       </c>
     </row>
     <row r="99" spans="1:4" ht="84">
-      <c r="A99" s="8" t="s">
+      <c r="A99" s="25" t="s">
         <v>2317</v>
       </c>
       <c r="B99" s="8" t="s">
@@ -20900,7 +20900,7 @@
       </c>
     </row>
     <row r="100" spans="1:4" ht="28">
-      <c r="A100" s="8" t="s">
+      <c r="A100" s="25" t="s">
         <v>2261</v>
       </c>
       <c r="B100" s="8" t="s">
@@ -20914,7 +20914,7 @@
       </c>
     </row>
     <row r="101" spans="1:4" ht="98">
-      <c r="A101" s="15" t="s">
+      <c r="A101" s="26" t="s">
         <v>2275</v>
       </c>
       <c r="B101" s="8" t="s">
@@ -20928,7 +20928,7 @@
       </c>
     </row>
     <row r="102" spans="1:4" ht="42">
-      <c r="A102" s="8" t="s">
+      <c r="A102" s="27" t="s">
         <v>2321</v>
       </c>
       <c r="B102" s="8" t="s">

--- a/inst/extdata/potato_db.xlsx
+++ b/inst/extdata/potato_db.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kimbrel1/Github/potato/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F9A319-F7E5-A546-B30C-4896F59BC882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBF66EF7-C0F1-B74C-95CA-0F1D80EA0970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="34960" yWindow="600" windowWidth="33840" windowHeight="28200" activeTab="2" xr2:uid="{CED2E7C7-DFF3-F648-B190-1601735D45BC}"/>
   </bookViews>
